--- a/lubrication_data.xlsx
+++ b/lubrication_data.xlsx
@@ -484,23 +484,45 @@
           <t>زيت محرك</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>98</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>مدة التشحيم: 98 يوم</t>
+          <t>آخر تشحيم: 2026-04-08</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>98</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>جديد - يحتاج تشحيم</t>
+          <t>✅ سليم - متبقي 98 أيام</t>
         </is>
       </c>
     </row>
